--- a/data_extactor/batch_10_fa/trimmed/batch_0023_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0023_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | زیست‌شناسی | حقوق و امور دولتی | ریاضیات | جغرافیا | ایمنی و امنیت عمومی</t>
+          <t>مدیریت و اداره | زیست‌شناسی | قانون و دولت | ریاضیات | جغرافیا | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان حفاظت از منابع طبیعی | چوب‌بُرها | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | بازرسان و کارشناسان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | کارگران جنگل‌داری و حفاظت | کارشناسان مدیریت مرتع</t>
+          <t>دانشمندان حفاظت از منابع طبیعی | درخت‌اندازان و چوب‌بُران جنگل | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | بازرسان و کارشناسان پیشگیری از حریق جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | مدیران و کارشناسان مدیریت مراتع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | علوم تجربی | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | زیست‌شناسی | پزشکی و دندانپزشکی | رایانه و الکترونیک | آموزش و تدریس | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>ریاضیات | زیست‌شناسی | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>هماهنگ‌کنندگان پژوهش‌های بالینی | متخصصان ژنتیک | کارشناسان آموزش بهداشت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | دانشمندان علوم پزشکی (به‌جز همه‌گیرشناسان) | میکروب‌شناسان | متخصصان پزشکی اجتماعی و پیشگیری</t>
+          <t>هماهنگ‌کنندگان کارآزمایی‌های بالینی | متخصصان ژنتیک | کارشناسان آموزش بهداشت و ارتقای سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | پژوهشگران و دانشمندان علوم پزشکی | میکروبیولوژیست‌ها | متخصصان پزشکی اجتماعی و طب پیشگیری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نگارش | علوم تجربی | یادگیری فعال | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>نگارش | علوم | یادگیری فعال | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | پزشکی و دندانپزشکی | شیمی | ریاضیات</t>
+          <t>زیست‌شناسی | زبان انگلیسی | پزشکی و دندان‌پزشکی | شیمی | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی</t>
+          <t>بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | متخصصان بیوانفورماتیک | هماهنگ‌کنندگان پژوهش‌های بالینی | همه‌گیرشناسان | متخصصان ژنتیک | میکروب‌شناسان | زیست‌شناسان مولکولی و سلولی</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | متخصصان بیوانفورماتیک | هماهنگ‌کنندگان کارآزمایی‌های بالینی | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | متخصصان ژنتیک | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم تجربی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | شیمی | ریاضیات | پزشکی و دندانپزشکی | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>زیست‌شناسی | شیمی | ریاضیات | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>زیست‌شناسان | میکروب‌شناسان | زیست‌شناسان مولکولی و سلولی | دانشمندان علوم پزشکی (به‌جز همه‌گیرشناسان) | متخصصان علوم دامی | متخصصان علوم خاک و گیاه‌شناسی | کارشناسان حفاظت از منابع طبیعی</t>
+          <t>زیست‌شناسان | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | پژوهشگران و دانشمندان علوم پزشکی | متخصصان علوم دامی | متخصصان خاک‌شناسی و علوم گیاهی | دانشمندان حفاظت از منابع طبیعی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم تجربی | نگارش | ریاضیات | تفکر انتقادی | شنیدن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | علوم | نگارش | ریاضیات | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>فیزیک | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | آموزش و تدریس | مهندسی و فناوری | شیمی</t>
+          <t>فیزیک | ریاضیات | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | مهندسی و فناوری | شیمی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | مهارت محاسباتی</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | استدلال ریاضی | توانایی عددی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دانشمندان علوم جوی و فضا | شیمی‌دانان | دانشمندان علوم رایانه و پژوهشگران فناوری اطلاعات | دانشمندان داده | ریاضی‌دانان | فیزیک‌دانان | مدرسان فیزیک در دانشگاه‌ها</t>
+          <t>دانشمندان و کارشناسان علوم جوی و فضا | شیمی‌دانان | پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | ریاضی‌دانان | فیزیک‌دانان | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>علوم تجربی | درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>علوم | درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>فیزیک | ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | آموزش و تدریس | شیمی</t>
+          <t>فیزیک | ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | شیمی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک کتبی | مهارت محاسباتی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی</t>
+          <t>استدلال ریاضی | درک کتبی | توانایی عددی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ستاره‌شناسان و اخترشناسان | شیمی‌دانان | دانشمندان داده | کارشناسان علوم مواد | ریاضی‌دانان | مهندسان هسته‌ای | مدرسان فیزیک در دانشگاه‌ها</t>
+          <t>ستاره‌شناسان و اخترشناسان | شیمی‌دانان | دانشمندان داده | کارشناسان و دانشمندان علوم مواد | ریاضی‌دانان | مهندسان هسته‌ای | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | یادگیری فعال | تفکر انتقادی | علوم تجربی | سخن گفتن | شنیدن فعال | نگارش | ریاضیات | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | یادگیری فعال | تفکر انتقادی | علوم | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تحلیل‌گران سیاست‌های تغییرات اقلیمی | دانشمندان داده | کارشناسان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی GIS | کارشناسان علوم زمین (به‌جز آب‌شناسان و جغرافیدانان) | کارشناسان هیدرولوژی و آب‌شناسی | فیزیک‌دانان | کارشناسان و متخصصان سنجش از دور</t>
+          <t>تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان داده | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | فیزیک‌دانان | دانشمندان و فناوران سنجش از دور</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>علوم تجربی | تفکر انتقادی | درک مطلب | سخن گفتن | شنیدن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>شیمی | ریاضیات | تولید و فرآوری | رایانه و الکترونیک | مدیریت و امور اداری | فیزیک</t>
+          <t>شیمی | ریاضیات | تولید و فرآوری | رایانه و الکترونیک | مدیریت و اداره | فیزیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان شیمی | تکنسین‌های شیمی | دانشمندان و کارشناسان صنایع غذایی | مهندسان مواد | کارشناسان علوم مواد | کارشناسان تحلیل و کنترل کیفیت</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان شیمی | تکنسین‌های شیمی | متخصصان و کارشناسان علوم و صنایع غذایی | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | کارشناسان تحلیل کنترل کیفیت</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم تجربی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | علوم | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | شیمی‌دانان | مهندسان صنایع | مهندسان ساخت و تولید | مهندسان مواد | مهندسان میکروسیستم | مهندسان سامانه‌های نانو</t>
+          <t>مهندسان شیمی | شیمی‌دانان | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان نانوسیستم‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | علوم تجربی | سخن گفتن | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | علوم | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | حقوق و امور دولتی | رایانه و الکترونیک | ایمنی و امنیت عمومی | شیمی | ریاضیات</t>
+          <t>زیست‌شناسی | قانون و دولت | رایانه و الکترونیک | ایمنی و امنیت عمومی | شیمی | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارشناسان حفاظت از منابع طبیعی | بازرسان انطباق محیط‌زیستی | مهندسان محیط زیست | کاردان‌ها و تکنسین‌های علوم محیطی و حفاظت (شامل بهداشت) | کارشناسان هیدرولوژی و آب‌شناسی | کارشناسان بهداشت و ایمنی حرفه‌ای | متخصصان منابع آب</t>
+          <t>دانشمندان حفاظت از منابع طبیعی | بازرسان رعایت ضوابط زیست‌محیطی | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | آب‌شناسان و هیدرولوژیست‌ها | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
